--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>118564572</v>
       </c>
       <c r="B4" t="n">
-        <v>96804</v>
+        <v>96811</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1502,6 +1502,521 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131735883</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5362</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>101728</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grön aspvedbock</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Saperda perforata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kärren Väst, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>579150</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6398324</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131733125</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101238</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kammartorp Väst, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>579346</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6398047</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131737000</v>
+      </c>
+      <c r="B11" t="n">
+        <v>75238</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kammartorp Väst, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>579356</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6398090</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På ek</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131732492</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91786</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kammarbogöl Nord, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>579297</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6398143</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131733587</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5027</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>101608</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Asppraktbagge</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecilonota variolosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Paykull, 1799)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kärren Väst, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>579244</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6398150</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spår i jätteasp. Ca 85-90 i brh.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -1507,7 +1507,7 @@
         <v>131735883</v>
       </c>
       <c r="B9" t="n">
-        <v>5362</v>
+        <v>5363</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>131733125</v>
       </c>
       <c r="B10" t="n">
-        <v>101238</v>
+        <v>101239</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>131737000</v>
       </c>
       <c r="B11" t="n">
-        <v>75238</v>
+        <v>75239</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>131732492</v>
       </c>
       <c r="B12" t="n">
-        <v>91786</v>
+        <v>91787</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>131733587</v>
       </c>
       <c r="B13" t="n">
-        <v>5027</v>
+        <v>5028</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -1608,7 +1608,7 @@
         <v>131733125</v>
       </c>
       <c r="B10" t="n">
-        <v>101239</v>
+        <v>101242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>131737000</v>
       </c>
       <c r="B11" t="n">
-        <v>75239</v>
+        <v>75242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>131732492</v>
       </c>
       <c r="B12" t="n">
-        <v>91787</v>
+        <v>91790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -1608,7 +1608,7 @@
         <v>131733125</v>
       </c>
       <c r="B10" t="n">
-        <v>101242</v>
+        <v>101243</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -1608,7 +1608,7 @@
         <v>131733125</v>
       </c>
       <c r="B10" t="n">
-        <v>101243</v>
+        <v>101249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>131737000</v>
       </c>
       <c r="B11" t="n">
-        <v>75242</v>
+        <v>75244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>131732492</v>
       </c>
       <c r="B12" t="n">
-        <v>91790</v>
+        <v>91796</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -1608,7 +1608,7 @@
         <v>131733125</v>
       </c>
       <c r="B10" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>131737000</v>
       </c>
       <c r="B11" t="n">
-        <v>75293</v>
+        <v>75295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>131732492</v>
       </c>
       <c r="B12" t="n">
-        <v>91847</v>
+        <v>91850</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 27737-2024 artfynd.xlsx
+++ b/artfynd/A 27737-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105920045</v>
+        <v>119624335</v>
       </c>
       <c r="B2" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5445</v>
+        <v>655</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,14 +717,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 765, Ankarsrums säteri, Sm</t>
+          <t>A 765, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579173.7927250455</v>
+        <v>579317</v>
       </c>
       <c r="R2" t="n">
-        <v>6398184.297483672</v>
+        <v>6398111</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105920013</v>
+        <v>119266053</v>
       </c>
       <c r="B3" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,16 +795,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5445</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,26 +814,26 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 765, Ankarsrums säteri, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579189.4288610672</v>
+        <v>579195</v>
       </c>
       <c r="R3" t="n">
-        <v>6398314.96151363</v>
+        <v>6398252</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,22 +860,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118564572</v>
+        <v>131734488</v>
       </c>
       <c r="B4" t="n">
-        <v>96816</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,42 +914,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 27737, Ankarsrums säteri, Sm</t>
+          <t>Kärren Sydväst, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579210</v>
+        <v>579272</v>
       </c>
       <c r="R4" t="n">
-        <v>6398292</v>
+        <v>6398140</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,12 +968,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,34 +987,32 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118608293</v>
+        <v>105920013</v>
       </c>
       <c r="B5" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,42 +1020,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kärren (Kärren), Sm</t>
+          <t>A 765, Ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579256</v>
+        <v>579189</v>
       </c>
       <c r="R5" t="n">
-        <v>6398133</v>
+        <v>6398315</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,22 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,33 +1099,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119266053</v>
+        <v>105920045</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,16 +1129,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5445</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1186,26 +1148,26 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>A 765, Ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579195</v>
+        <v>579174</v>
       </c>
       <c r="R6" t="n">
-        <v>6398252</v>
+        <v>6398184</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,22 +1194,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2023-01-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,15 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119624115</v>
+        <v>118564416</v>
       </c>
       <c r="B7" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,42 +1238,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5445</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 27727, Ankarsrum, Sm</t>
+          <t>A 27737, Ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579298</v>
+        <v>579165</v>
       </c>
       <c r="R7" t="n">
-        <v>6398158</v>
+        <v>6398368</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,17 +1303,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I asp</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,6 +1317,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1390,15 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119624335</v>
+        <v>131732492</v>
       </c>
       <c r="B8" t="n">
-        <v>89441</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91932</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,45 +1347,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>655</v>
+        <v>5445</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fistulina hepatica</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) With., nom sanct.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 765, Ankarsrum, Sm</t>
+          <t>Kammarbogöl Nord, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579317</v>
+        <v>579297</v>
       </c>
       <c r="R8" t="n">
-        <v>6398111</v>
+        <v>6398143</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,12 +1401,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,64 +1415,67 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131735883</v>
+        <v>131737000</v>
       </c>
       <c r="B9" t="n">
-        <v>5364</v>
+        <v>75340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101728</v>
+        <v>6428</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kärren Väst, Sm</t>
+          <t>Kammartorp Väst, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579150</v>
+        <v>579356</v>
       </c>
       <c r="R9" t="n">
-        <v>6398324</v>
+        <v>6398090</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,6 +1508,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På ek</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131733125</v>
+        <v>118608293</v>
       </c>
       <c r="B10" t="n">
-        <v>101304</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,37 +1554,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kammartorp Väst, Sm</t>
+          <t>Kärren, Kärren, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579346</v>
+        <v>579256</v>
       </c>
       <c r="R10" t="n">
-        <v>6398047</v>
+        <v>6398133</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,12 +1613,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,26 +1643,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131737000</v>
+        <v>118608477</v>
       </c>
       <c r="B11" t="n">
-        <v>75295</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,37 +1666,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6428</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kammartorp Väst, Sm</t>
+          <t>Kammarbogöl, Kammarbogöl, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579356</v>
+        <v>579312</v>
       </c>
       <c r="R11" t="n">
-        <v>6398090</v>
+        <v>6398154</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,17 +1725,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På ek</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,61 +1755,65 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131732492</v>
+        <v>119624115</v>
       </c>
       <c r="B12" t="n">
-        <v>91850</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5445</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kammarbogöl Nord, Sm</t>
+          <t>A 27727, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579297</v>
+        <v>579298</v>
       </c>
       <c r="R12" t="n">
-        <v>6398143</v>
+        <v>6398158</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,12 +1840,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>I asp</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,61 +1865,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131733587</v>
+        <v>118564572</v>
       </c>
       <c r="B13" t="n">
-        <v>5029</v>
+        <v>97986</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101608</v>
+        <v>221946</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kärren Väst, Sm</t>
+          <t>A 27737, Ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579244</v>
+        <v>579210</v>
       </c>
       <c r="R13" t="n">
-        <v>6398150</v>
+        <v>6398292</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,17 +1950,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spår i jätteasp. Ca 85-90 i brh.</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,21 +1964,119 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131733125</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kammartorp Väst, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>579346</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6398047</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Helene Andersson</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr">
+      <c r="AY14" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
